--- a/Reseau_projet/Table d'addressage.xlsx
+++ b/Reseau_projet/Table d'addressage.xlsx
@@ -5,22 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mustafa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mustafa\Desktop\Reseau_projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12750F31-80A8-460A-AA01-C6DB97D4753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1781B3F1-3300-45F4-A132-3EE1AAB57F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table daddressage" sheetId="1" r:id="rId1"/>
+    <sheet name="Diagramme des flux" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
   <si>
     <t>Périphériques</t>
   </si>
@@ -134,13 +135,118 @@
   </si>
   <si>
     <t>DMZ (mat)</t>
+  </si>
+  <si>
+    <t>FLUX</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>DESTINATION</t>
+  </si>
+  <si>
+    <t>PROTOCOLE</t>
+  </si>
+  <si>
+    <t>ACL</t>
+  </si>
+  <si>
+    <t>INTERNET</t>
+  </si>
+  <si>
+    <t>TCP 80/443</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Accéder à internet depuis un guest</t>
+  </si>
+  <si>
+    <t>GUEST-INTERNET</t>
+  </si>
+  <si>
+    <t>GUEST-INTERNE</t>
+  </si>
+  <si>
+    <t>TOUT</t>
+  </si>
+  <si>
+    <t>192.168.0.0 (reseau interne)</t>
+  </si>
+  <si>
+    <t>BLOQUE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>Bloque tout guest essayant d'accèder au réseau interne</t>
+  </si>
+  <si>
+    <t>GUEST-IP</t>
+  </si>
+  <si>
+    <t>VLAN x</t>
+  </si>
+  <si>
+    <t>UDP 67/68</t>
+  </si>
+  <si>
+    <t>Le DHCP envoie une ip aux utilisateurs se connectat au reseau</t>
+  </si>
+  <si>
+    <t>INTERNE-INTERNET</t>
+  </si>
+  <si>
+    <t>192.168.x.x</t>
+  </si>
+  <si>
+    <t>INTERNET-INTERNE</t>
+  </si>
+  <si>
+    <t>TOUT IP</t>
+  </si>
+  <si>
+    <t>192.168.x.x (réseau interne)</t>
+  </si>
+  <si>
+    <t>Toute requete vers le réseau interne est bloqué</t>
+  </si>
+  <si>
+    <t>VLAN-VLAN</t>
+  </si>
+  <si>
+    <t>192.168.x.x (sauf .20.x)</t>
+  </si>
+  <si>
+    <t>ICMP</t>
+  </si>
+  <si>
+    <t>Les vlans peuvent se ping, sauf le guest</t>
+  </si>
+  <si>
+    <t>VLAN 40 (192.168.20.x /24)</t>
+  </si>
+  <si>
+    <t>Les utilisateurs du réseau peuvent acceder à internet</t>
+  </si>
+  <si>
+    <t>INTERNE-DNS</t>
+  </si>
+  <si>
+    <t>UDP 53</t>
+  </si>
+  <si>
+    <t>Resolution de nom de domaine</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -159,6 +265,21 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial"/>
@@ -186,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -200,26 +321,156 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="12">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -245,13 +496,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Table daddressage-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -276,6 +543,21 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Passerelle par défaut"/>
   </tableColumns>
   <tableStyleInfo name="Table daddressage-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4B240A74-93B2-45E4-8DCD-FC7CA376320A}" name="Tableau2" displayName="Tableau2" ref="A1:F8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F8" xr:uid="{4B240A74-93B2-45E4-8DCD-FC7CA376320A}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{8BDCD2C7-2C50-4353-B70A-79D70F19F7AB}" name="FLUX" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{56BB49E6-2641-4818-BD05-8473AD3AB5D3}" name="SOURCE" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{51CE9A5A-9743-4371-982A-FCF5FF4A8F69}" name="DESTINATION" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{8F7DFF69-BCC1-47CF-833F-7E05CED9D221}" name="PROTOCOLE" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{A484DCCD-5ACD-4E94-B3DB-2AAB803FEC99}" name="ACL" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E3E87C61-0082-4B62-A9EF-161C77BBCE70}" name="DESCRIPTION" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="Table daddressage-style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -714,4 +996,184 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FE87A2-B1B6-4863-9C72-DF50C15CE8B6}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="54.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>